--- a/측정문항_2025-1118_충남대학교 창의융합대학.xlsx
+++ b/측정문항_2025-1118_충남대학교 창의융합대학.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\cnu_jongdan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\CNU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14EC864F-1BD0-482D-9600-2E88F8B84468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B56DD4A-3891-4A2A-9A21-8A917F2EC619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5EC9AEF6-43F7-408C-BC46-DED5B93B7013}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5EC9AEF6-43F7-408C-BC46-DED5B93B7013}"/>
   </bookViews>
   <sheets>
     <sheet name="안내문" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="425">
   <si>
     <t>측정 영역</t>
   </si>
@@ -504,9 +504,6 @@
     <t>아래 비교과 프로그램을 알고 있습니까? (복수 선택)</t>
   </si>
   <si>
-    <t>지난 한 학기 동안 참여한 비교과 프로그램을 모두 선택하세요.</t>
-  </si>
-  <si>
     <t>비교과 총 참여 횟수</t>
   </si>
   <si>
@@ -528,9 +525,6 @@
     <t>비교과 프로그램이 탐색 분반 선택에 도움이 되었습니까?</t>
   </si>
   <si>
-    <t>전공 탐색에 있어 추가적으로 도움을 받았으면 하는 부분을 작성해주세요(선택)</t>
-  </si>
-  <si>
     <t>상담/지원 이용</t>
   </si>
   <si>
@@ -553,14 +547,6 @@
   </si>
   <si>
     <t>비고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>참여가 어려웠던 구체적 이유를 작성해주세요(선택)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>학내 1:1 상담에 대해 요청 사항이나 추가적으로 필요한 점은 무엇인지 작성해주세요(선택)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2124,15 +2110,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>❑ 있다.(1지망 학과 선택)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>창의융합대학 입학자만 응답.
-지망 학과의 경우 학과 리스트 정보 전달 시 업데이트 예정</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>다음 문항을 잘 읽고 올해 1년 동안 있었던 일을 떠올리며 학교 생활을 하며 경험한 내용을 토대로 문항에 응답해주세요. 잘 기억이 나지 않는다면, 가장 가까운 응답을 해주시 바랍니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2288,10 +2265,6 @@
   </si>
   <si>
     <t>학사(성적) 경고 또는 직전 안내를 받은 적이 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>선택사항. 민감정보입력</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2742,6 +2715,26 @@
   </si>
   <si>
     <t>공정하다고 느낀 상황에 대해 간단하게 작성해주세요.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>❑ 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>지난 한 학기 동안 참여한 비교과 프로그램을 모두 선택하세요.(복수 선택)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>전공 탐색에 있어 추가적으로 도움을 받았으면 하는 부분을 작성해주세요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>참여가 어려웠던 구체적 이유를 작성해주세요.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>학내 1:1 상담에 대해 요청 사항이나 추가적으로 필요한 점은 무엇인지 작성해주세요.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3722,26 +3715,44 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3756,18 +3767,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3782,11 +3781,32 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3806,32 +3826,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3846,33 +3866,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4230,7 +4223,7 @@
     </row>
     <row r="2" spans="2:8" ht="20.25" thickBot="1">
       <c r="B2" s="72" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C2" s="72"/>
       <c r="D2" s="72"/>
@@ -4241,7 +4234,7 @@
     </row>
     <row r="3" spans="2:8" ht="363" customHeight="1" thickBot="1">
       <c r="B3" s="71" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
@@ -4261,7 +4254,7 @@
     </row>
     <row r="5" spans="2:8" ht="19.5">
       <c r="B5" s="73" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C5" s="73"/>
       <c r="D5" s="73"/>
@@ -4272,7 +4265,7 @@
     </row>
     <row r="6" spans="2:8" ht="19.5">
       <c r="B6" s="73" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C6" s="73"/>
       <c r="D6" s="73"/>
@@ -4283,7 +4276,7 @@
     </row>
     <row r="7" spans="2:8" ht="19.5">
       <c r="B7" s="73" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C7" s="73"/>
       <c r="D7" s="73"/>
@@ -4381,37 +4374,37 @@
   <sheetData>
     <row r="1" spans="1:9" ht="55.5" customHeight="1" thickBot="1">
       <c r="A1" s="26" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="77" t="s">
-        <v>323</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="78"/>
+      <c r="B2" s="76" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:9" ht="51" customHeight="1" thickBot="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="80"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="79"/>
     </row>
     <row r="4" spans="1:9" ht="28.5">
       <c r="A4" s="29" t="s">
@@ -4427,2058 +4420,2053 @@
         <v>3</v>
       </c>
       <c r="E4" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>175</v>
-      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="80" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E5" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I5" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>180</v>
-      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="74"/>
-      <c r="B6" s="74"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="80"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E6" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>180</v>
-      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="74"/>
-      <c r="B7" s="74"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="80"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F7" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="74"/>
-      <c r="B8" s="74"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="80"/>
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I8" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="74"/>
-      <c r="B9" s="74"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="E9" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="74"/>
-      <c r="B10" s="74"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="80"/>
       <c r="C10" s="1">
         <v>6</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E10" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F10" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="74"/>
-      <c r="B11" s="74"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="1">
         <v>7</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="E11" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I11" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F11" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="74"/>
-      <c r="B12" s="74"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="1">
         <v>8</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E12" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F12" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="74"/>
-      <c r="B13" s="74" t="s">
+      <c r="A13" s="80"/>
+      <c r="B13" s="80" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="1">
         <v>9</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="E13" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I13" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="80"/>
       <c r="C14" s="1">
         <v>10</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="E14" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I14" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F14" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="74"/>
-      <c r="B15" s="74"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="1">
         <v>11</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="E15" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I15" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="74"/>
-      <c r="B16" s="74"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="1">
         <v>12</v>
       </c>
       <c r="D16" s="31" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="E16" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F16" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="74"/>
-      <c r="B17" s="74"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="80"/>
       <c r="C17" s="1">
         <v>13</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E17" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F17" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G17" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H17" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I17" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="74"/>
-      <c r="B18" s="74"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="1">
         <v>14</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E18" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I18" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F18" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G18" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="74"/>
-      <c r="B19" s="74"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="1">
         <v>15</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E19" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F19" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="74"/>
-      <c r="B20" s="74"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="80"/>
       <c r="C20" s="1">
         <v>16</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E20" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I20" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I20" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="74" t="s">
+      <c r="A21" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="74" t="s">
+      <c r="B21" s="80" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="1">
         <v>17</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="E21" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I21" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F21" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G21" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H21" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="74"/>
-      <c r="B22" s="74"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="80"/>
       <c r="C22" s="1">
         <v>18</v>
       </c>
       <c r="D22" s="31" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E22" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I22" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F22" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G22" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H22" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="74"/>
-      <c r="B23" s="74"/>
+      <c r="A23" s="80"/>
+      <c r="B23" s="80"/>
       <c r="C23" s="1">
         <v>19</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E23" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I23" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G23" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H23" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="74"/>
-      <c r="B24" s="74"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="80"/>
       <c r="C24" s="1">
         <v>20</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E24" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G24" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="1">
         <v>21</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="E25" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H25" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
+      <c r="A26" s="80"/>
+      <c r="B26" s="80"/>
       <c r="C26" s="1">
         <v>22</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E26" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I26" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F26" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G26" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H26" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="74"/>
-      <c r="B27" s="74"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="1">
         <v>23</v>
       </c>
       <c r="D27" s="31" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="E27" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I27" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F27" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G27" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H27" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
+      <c r="A28" s="80"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="1">
         <v>24</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="E28" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I28" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F28" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G28" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="80" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="1">
         <v>25</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E29" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F29" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G29" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="74"/>
-      <c r="B30" s="74"/>
+      <c r="A30" s="80"/>
+      <c r="B30" s="80"/>
       <c r="C30" s="1">
         <v>26</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E30" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I30" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F30" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G30" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I30" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
+      <c r="A31" s="80"/>
+      <c r="B31" s="80"/>
       <c r="C31" s="1">
         <v>27</v>
       </c>
       <c r="D31" s="31" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E31" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I31" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F31" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G31" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I31" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="74"/>
-      <c r="B32" s="74"/>
+      <c r="A32" s="80"/>
+      <c r="B32" s="80"/>
       <c r="C32" s="1">
         <v>28</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="E32" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I32" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F32" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G32" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="74"/>
-      <c r="B33" s="74"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="1">
         <v>29</v>
       </c>
       <c r="D33" s="31" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="E33" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I33" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G33" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I33" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="74"/>
-      <c r="B34" s="74"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="80"/>
       <c r="C34" s="1">
         <v>30</v>
       </c>
       <c r="D34" s="31" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="E34" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F34" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G34" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H34" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="74"/>
-      <c r="B35" s="74"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="80"/>
       <c r="C35" s="1">
         <v>31</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E35" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I35" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F35" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="74"/>
-      <c r="B36" s="74"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="1">
         <v>32</v>
       </c>
       <c r="D36" s="31" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E36" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F36" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G36" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I36" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="74"/>
-      <c r="B37" s="74" t="s">
+      <c r="A37" s="80"/>
+      <c r="B37" s="80" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="1">
         <v>33</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E37" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H37" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I37" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F37" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G37" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H37" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I37" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="74"/>
-      <c r="B38" s="74"/>
+      <c r="A38" s="80"/>
+      <c r="B38" s="80"/>
       <c r="C38" s="1">
         <v>34</v>
       </c>
       <c r="D38" s="31" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E38" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G38" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H38" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I38" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F38" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G38" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H38" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I38" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="74"/>
-      <c r="B39" s="74"/>
+      <c r="A39" s="80"/>
+      <c r="B39" s="80"/>
       <c r="C39" s="1">
         <v>35</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="E39" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I39" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F39" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G39" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I39" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="74"/>
-      <c r="B40" s="74"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
       <c r="C40" s="1">
         <v>36</v>
       </c>
       <c r="D40" s="31" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="E40" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H40" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F40" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G40" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H40" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I40" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="74"/>
-      <c r="B41" s="74"/>
+      <c r="A41" s="80"/>
+      <c r="B41" s="80"/>
       <c r="C41" s="1">
         <v>37</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E41" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G41" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I41" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F41" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G41" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H41" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I41" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
       <c r="C42" s="1">
         <v>38</v>
       </c>
       <c r="D42" s="31" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E42" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G42" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I42" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I42" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="74"/>
-      <c r="B43" s="74"/>
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
       <c r="C43" s="1">
         <v>39</v>
       </c>
       <c r="D43" s="31" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="E43" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H43" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F43" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G43" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H43" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I43" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="74"/>
-      <c r="B44" s="74"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
       <c r="C44" s="1">
         <v>40</v>
       </c>
       <c r="D44" s="31" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="E44" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H44" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I44" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F44" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G44" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H44" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I44" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="74"/>
-      <c r="B45" s="74" t="s">
+      <c r="A45" s="80"/>
+      <c r="B45" s="80" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="1">
         <v>41</v>
       </c>
       <c r="D45" s="31" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="E45" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H45" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I45" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F45" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G45" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H45" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I45" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="74"/>
-      <c r="B46" s="74"/>
+      <c r="A46" s="80"/>
+      <c r="B46" s="80"/>
       <c r="C46" s="1">
         <v>42</v>
       </c>
       <c r="D46" s="31" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="E46" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I46" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F46" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G46" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H46" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I46" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="74"/>
-      <c r="B47" s="74"/>
+      <c r="A47" s="80"/>
+      <c r="B47" s="80"/>
       <c r="C47" s="1">
         <v>43</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E47" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G47" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H47" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I47" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F47" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I47" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="74"/>
-      <c r="B48" s="74"/>
+      <c r="A48" s="80"/>
+      <c r="B48" s="80"/>
       <c r="C48" s="1">
         <v>44</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="E48" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I48" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F48" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G48" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H48" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I48" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="74"/>
-      <c r="B49" s="74"/>
+      <c r="A49" s="80"/>
+      <c r="B49" s="80"/>
       <c r="C49" s="1">
         <v>45</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="E49" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H49" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I49" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F49" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G49" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H49" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I49" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="74"/>
-      <c r="B50" s="74"/>
+      <c r="A50" s="80"/>
+      <c r="B50" s="80"/>
       <c r="C50" s="1">
         <v>46</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E50" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I50" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F50" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G50" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H50" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I50" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="74"/>
-      <c r="B51" s="74"/>
+      <c r="A51" s="80"/>
+      <c r="B51" s="80"/>
       <c r="C51" s="1">
         <v>47</v>
       </c>
       <c r="D51" s="31" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="E51" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H51" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I51" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F51" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G51" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H51" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I51" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="74"/>
-      <c r="B52" s="74"/>
+      <c r="A52" s="80"/>
+      <c r="B52" s="80"/>
       <c r="C52" s="1">
         <v>48</v>
       </c>
       <c r="D52" s="31" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E52" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I52" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F52" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H52" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I52" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="74" t="s">
+      <c r="A53" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="74" t="s">
+      <c r="B53" s="80" t="s">
         <v>14</v>
       </c>
       <c r="C53" s="1">
         <v>49</v>
       </c>
       <c r="D53" s="31" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="E53" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H53" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I53" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G53" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H53" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I53" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="74"/>
-      <c r="B54" s="74"/>
+      <c r="A54" s="80"/>
+      <c r="B54" s="80"/>
       <c r="C54" s="1">
         <v>50</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="E54" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H54" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I54" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F54" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H54" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I54" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="74"/>
-      <c r="B55" s="74"/>
+      <c r="A55" s="80"/>
+      <c r="B55" s="80"/>
       <c r="C55" s="1">
         <v>51</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="E55" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G55" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H55" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I55" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F55" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G55" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H55" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I55" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="74"/>
-      <c r="B56" s="74"/>
+      <c r="A56" s="80"/>
+      <c r="B56" s="80"/>
       <c r="C56" s="1">
         <v>52</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="E56" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G56" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H56" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I56" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F56" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G56" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H56" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I56" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="74"/>
-      <c r="B57" s="74"/>
+      <c r="A57" s="80"/>
+      <c r="B57" s="80"/>
       <c r="C57" s="1">
         <v>53</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="E57" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G57" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I57" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F57" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G57" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H57" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I57" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="74"/>
-      <c r="B58" s="74"/>
+      <c r="A58" s="80"/>
+      <c r="B58" s="80"/>
       <c r="C58" s="1">
         <v>54</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E58" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H58" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I58" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F58" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G58" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H58" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I58" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="74"/>
-      <c r="B59" s="74"/>
+      <c r="A59" s="80"/>
+      <c r="B59" s="80"/>
       <c r="C59" s="1">
         <v>55</v>
       </c>
       <c r="D59" s="31" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="E59" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G59" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H59" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I59" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F59" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G59" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H59" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I59" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="74"/>
-      <c r="B60" s="74"/>
+      <c r="A60" s="80"/>
+      <c r="B60" s="80"/>
       <c r="C60" s="1">
         <v>56</v>
       </c>
       <c r="D60" s="31" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E60" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H60" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I60" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F60" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G60" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H60" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I60" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="74"/>
-      <c r="B61" s="74" t="s">
+      <c r="A61" s="80"/>
+      <c r="B61" s="80" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="1">
         <v>57</v>
       </c>
       <c r="D61" s="31" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="E61" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G61" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H61" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I61" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F61" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G61" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H61" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I61" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="74"/>
-      <c r="B62" s="74"/>
+      <c r="A62" s="80"/>
+      <c r="B62" s="80"/>
       <c r="C62" s="1">
         <v>58</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="E62" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F62" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H62" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I62" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F62" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G62" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H62" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I62" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="74"/>
-      <c r="B63" s="74"/>
+      <c r="A63" s="80"/>
+      <c r="B63" s="80"/>
       <c r="C63" s="1">
         <v>59</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="E63" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G63" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I63" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F63" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G63" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H63" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I63" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="74"/>
-      <c r="B64" s="74"/>
+      <c r="A64" s="80"/>
+      <c r="B64" s="80"/>
       <c r="C64" s="1">
         <v>60</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E64" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G64" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H64" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I64" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F64" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G64" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H64" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I64" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="65" spans="1:9">
-      <c r="A65" s="74"/>
-      <c r="B65" s="74"/>
+      <c r="A65" s="80"/>
+      <c r="B65" s="80"/>
       <c r="C65" s="1">
         <v>61</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="E65" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G65" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H65" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I65" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F65" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G65" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H65" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I65" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="74"/>
-      <c r="B66" s="74"/>
+      <c r="A66" s="80"/>
+      <c r="B66" s="80"/>
       <c r="C66" s="1">
         <v>62</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="E66" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H66" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I66" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F66" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G66" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H66" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I66" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="74"/>
-      <c r="B67" s="74"/>
+      <c r="A67" s="80"/>
+      <c r="B67" s="80"/>
       <c r="C67" s="1">
         <v>63</v>
       </c>
       <c r="D67" s="31" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E67" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G67" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H67" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I67" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F67" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G67" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H67" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I67" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="74"/>
-      <c r="B68" s="74"/>
+      <c r="A68" s="80"/>
+      <c r="B68" s="80"/>
       <c r="C68" s="1">
         <v>64</v>
       </c>
       <c r="D68" s="31" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E68" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G68" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H68" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I68" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F68" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G68" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H68" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I68" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="74" t="s">
+      <c r="A69" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="B69" s="74" t="s">
+      <c r="B69" s="80" t="s">
         <v>17</v>
       </c>
       <c r="C69" s="1">
         <v>65</v>
       </c>
       <c r="D69" s="31" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E69" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I69" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F69" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H69" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I69" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="74"/>
-      <c r="B70" s="74"/>
+      <c r="A70" s="80"/>
+      <c r="B70" s="80"/>
       <c r="C70" s="1">
         <v>66</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="E70" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H70" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I70" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F70" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H70" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I70" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="74"/>
-      <c r="B71" s="74"/>
+      <c r="A71" s="80"/>
+      <c r="B71" s="80"/>
       <c r="C71" s="1">
         <v>67</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E71" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G71" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H71" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I71" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F71" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G71" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H71" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I71" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="74"/>
-      <c r="B72" s="74"/>
+      <c r="A72" s="80"/>
+      <c r="B72" s="80"/>
       <c r="C72" s="1">
         <v>68</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E72" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H72" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I72" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F72" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H72" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I72" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="74"/>
-      <c r="B73" s="74"/>
+      <c r="A73" s="80"/>
+      <c r="B73" s="80"/>
       <c r="C73" s="1">
         <v>69</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E73" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G73" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H73" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I73" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F73" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G73" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H73" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I73" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="74"/>
-      <c r="B74" s="74"/>
+      <c r="A74" s="80"/>
+      <c r="B74" s="80"/>
       <c r="C74" s="1">
         <v>70</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E74" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F74" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G74" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H74" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I74" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F74" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G74" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H74" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I74" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="74"/>
-      <c r="B75" s="74"/>
+      <c r="A75" s="80"/>
+      <c r="B75" s="80"/>
       <c r="C75" s="1">
         <v>71</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E75" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G75" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H75" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I75" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F75" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G75" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H75" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I75" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="76" spans="1:9">
-      <c r="A76" s="74"/>
-      <c r="B76" s="74"/>
+      <c r="A76" s="80"/>
+      <c r="B76" s="80"/>
       <c r="C76" s="1">
         <v>72</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E76" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F76" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G76" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H76" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I76" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F76" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G76" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H76" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I76" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="74"/>
-      <c r="B77" s="74" t="s">
+      <c r="A77" s="80"/>
+      <c r="B77" s="80" t="s">
         <v>18</v>
       </c>
       <c r="C77" s="1">
         <v>73</v>
       </c>
       <c r="D77" s="31" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E77" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F77" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H77" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I77" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F77" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G77" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H77" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I77" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="74"/>
-      <c r="B78" s="74"/>
+      <c r="A78" s="80"/>
+      <c r="B78" s="80"/>
       <c r="C78" s="1">
         <v>74</v>
       </c>
       <c r="D78" s="31" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="E78" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F78" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G78" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H78" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I78" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F78" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G78" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H78" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I78" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="74"/>
-      <c r="B79" s="74"/>
+      <c r="A79" s="80"/>
+      <c r="B79" s="80"/>
       <c r="C79" s="1">
         <v>75</v>
       </c>
       <c r="D79" s="31" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="E79" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F79" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G79" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H79" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I79" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F79" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G79" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H79" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I79" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" s="74"/>
-      <c r="B80" s="74"/>
+      <c r="A80" s="80"/>
+      <c r="B80" s="80"/>
       <c r="C80" s="1">
         <v>76</v>
       </c>
       <c r="D80" s="31" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="E80" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F80" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H80" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I80" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F80" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G80" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H80" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I80" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="74"/>
-      <c r="B81" s="74"/>
+      <c r="A81" s="80"/>
+      <c r="B81" s="80"/>
       <c r="C81" s="1">
         <v>77</v>
       </c>
       <c r="D81" s="31" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E81" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F81" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G81" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H81" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I81" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F81" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G81" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H81" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I81" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="82" spans="1:9">
-      <c r="A82" s="74"/>
-      <c r="B82" s="74"/>
+      <c r="A82" s="80"/>
+      <c r="B82" s="80"/>
       <c r="C82" s="1">
         <v>78</v>
       </c>
       <c r="D82" s="31" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E82" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G82" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H82" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I82" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F82" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G82" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H82" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I82" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="74"/>
-      <c r="B83" s="74"/>
+      <c r="A83" s="80"/>
+      <c r="B83" s="80"/>
       <c r="C83" s="1">
         <v>79</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="E83" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F83" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G83" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H83" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I83" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F83" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G83" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H83" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I83" s="28" t="s">
-        <v>185</v>
-      </c>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="74"/>
-      <c r="B84" s="74"/>
+      <c r="A84" s="80"/>
+      <c r="B84" s="80"/>
       <c r="C84" s="1">
         <v>80</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="E84" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F84" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G84" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H84" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I84" s="28" t="s">
         <v>181</v>
-      </c>
-      <c r="F84" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="G84" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="H84" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I84" s="28" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="A53:A68"/>
-    <mergeCell ref="B53:B60"/>
-    <mergeCell ref="B61:B68"/>
     <mergeCell ref="A69:A84"/>
     <mergeCell ref="B69:B76"/>
     <mergeCell ref="B77:B84"/>
@@ -6491,6 +6479,11 @@
     <mergeCell ref="B29:B36"/>
     <mergeCell ref="B37:B44"/>
     <mergeCell ref="B45:B52"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="A53:A68"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="B61:B68"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6513,32 +6506,32 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" thickBot="1">
       <c r="A1" s="26" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17.25" thickTop="1">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="81" t="s">
-        <v>318</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="82"/>
+      <c r="B2" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="88"/>
     </row>
     <row r="3" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="84"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="18" thickTop="1">
       <c r="A4" s="32" t="s">
@@ -6550,854 +6543,875 @@
       <c r="C4" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="92" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="92"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
+      <c r="D4" s="94" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="94"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="80" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F5" s="34"/>
       <c r="G5" s="35"/>
       <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="74"/>
-      <c r="B6" s="74"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="80"/>
       <c r="C6" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="74"/>
-      <c r="B7" s="74"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="80"/>
       <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="85"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="88"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="84"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="74"/>
-      <c r="B8" s="74" t="s">
+      <c r="A8" s="80"/>
+      <c r="B8" s="80" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="35"/>
       <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="74"/>
-      <c r="B9" s="74"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="74"/>
-      <c r="B10" s="74"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="80"/>
       <c r="C10" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D10" s="85"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="87"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="88"/>
+        <v>415</v>
+      </c>
+      <c r="D10" s="81"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="84"/>
     </row>
     <row r="11" spans="1:8" ht="31.5">
-      <c r="A11" s="74"/>
-      <c r="B11" s="74" t="s">
+      <c r="A11" s="80"/>
+      <c r="B11" s="80" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="35"/>
       <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="74"/>
-      <c r="B12" s="74"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="2" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="74"/>
-      <c r="B13" s="74"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="80"/>
       <c r="C13" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="88"/>
+        <v>419</v>
+      </c>
+      <c r="D13" s="81"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="84"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74" t="s">
+      <c r="A14" s="80"/>
+      <c r="B14" s="80" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="35"/>
       <c r="H14" s="36"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="74"/>
-      <c r="B15" s="74"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="74"/>
-      <c r="B16" s="74"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="85"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="88"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="84"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="74"/>
-      <c r="B17" s="74" t="s">
+      <c r="A17" s="80"/>
+      <c r="B17" s="80" t="s">
         <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="74"/>
-      <c r="B18" s="74"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="74"/>
-      <c r="B19" s="74"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="85"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="88"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
+      <c r="H19" s="84"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="74"/>
-      <c r="B20" s="74" t="s">
+      <c r="A20" s="80"/>
+      <c r="B20" s="80" t="s">
         <v>36</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="35"/>
       <c r="H20" s="36"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="74"/>
-      <c r="B21" s="74"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="80"/>
       <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E21" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="74"/>
-      <c r="B22" s="74"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="80"/>
       <c r="C22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="85"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="88"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="83"/>
+      <c r="G22" s="83"/>
+      <c r="H22" s="84"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="74"/>
-      <c r="B23" s="74" t="s">
+      <c r="A23" s="80"/>
+      <c r="B23" s="80" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F23" s="34"/>
       <c r="G23" s="35"/>
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="74"/>
-      <c r="B24" s="74"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="80"/>
       <c r="C24" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="85" t="s">
-        <v>164</v>
-      </c>
-      <c r="E25" s="86"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="88"/>
+      <c r="D25" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="82"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="83"/>
+      <c r="H25" s="84"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74" t="s">
+      <c r="A26" s="80"/>
+      <c r="B26" s="80" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F26" s="34"/>
       <c r="G26" s="35"/>
       <c r="H26" s="36"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="74"/>
-      <c r="B27" s="74"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="80"/>
       <c r="C27" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E27" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H27" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
+      <c r="A28" s="80"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="85"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="87"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="88"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="84"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="80" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F29" s="34"/>
       <c r="G29" s="35"/>
       <c r="H29" s="36"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="74"/>
-      <c r="B30" s="74"/>
+      <c r="A30" s="80"/>
+      <c r="B30" s="80"/>
       <c r="C30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H30" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="74"/>
-      <c r="B31" s="74"/>
+      <c r="A31" s="80"/>
+      <c r="B31" s="80"/>
       <c r="C31" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D31" s="85"/>
-      <c r="E31" s="86"/>
-      <c r="F31" s="87"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="88"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="82"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="84"/>
     </row>
     <row r="32" spans="1:8" ht="31.5">
-      <c r="A32" s="74"/>
-      <c r="B32" s="74" t="s">
+      <c r="A32" s="80"/>
+      <c r="B32" s="80" t="s">
         <v>50</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F32" s="34"/>
       <c r="G32" s="35"/>
       <c r="H32" s="36"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="74"/>
-      <c r="B33" s="74"/>
+      <c r="A33" s="80"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="74"/>
-      <c r="B34" s="74"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="80"/>
       <c r="C34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="85"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="87"/>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="82"/>
+      <c r="F34" s="83"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="84"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="74"/>
-      <c r="B35" s="74" t="s">
+      <c r="A35" s="80"/>
+      <c r="B35" s="80" t="s">
         <v>51</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F35" s="34"/>
       <c r="G35" s="35"/>
       <c r="H35" s="36"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="74"/>
-      <c r="B36" s="74"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F36" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G36" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H36" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="74"/>
-      <c r="B37" s="74"/>
+      <c r="A37" s="80"/>
+      <c r="B37" s="80"/>
       <c r="C37" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="85"/>
-      <c r="E37" s="86"/>
-      <c r="F37" s="87"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="88"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="83"/>
+      <c r="G37" s="83"/>
+      <c r="H37" s="84"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="74"/>
-      <c r="B38" s="74" t="s">
+      <c r="A38" s="80"/>
+      <c r="B38" s="80" t="s">
         <v>52</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F38" s="34"/>
       <c r="G38" s="35"/>
       <c r="H38" s="36"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="74"/>
-      <c r="B39" s="74"/>
+      <c r="A39" s="80"/>
+      <c r="B39" s="80"/>
       <c r="C39" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H39" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="74"/>
-      <c r="B40" s="74"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
       <c r="C40" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="85"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="87"/>
-      <c r="G40" s="87"/>
-      <c r="H40" s="88"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="83"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="84"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="74"/>
-      <c r="B41" s="74" t="s">
+      <c r="A41" s="80"/>
+      <c r="B41" s="80" t="s">
         <v>53</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F41" s="34"/>
       <c r="G41" s="35"/>
       <c r="H41" s="36"/>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="74"/>
-      <c r="B42" s="74"/>
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
       <c r="C42" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G42" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="74"/>
-      <c r="B43" s="74"/>
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
       <c r="C43" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="85"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="87"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="88"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="82"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="84"/>
     </row>
     <row r="44" spans="1:8" ht="31.5">
-      <c r="A44" s="74"/>
-      <c r="B44" s="74" t="s">
+      <c r="A44" s="80"/>
+      <c r="B44" s="80" t="s">
         <v>54</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F44" s="34"/>
       <c r="G44" s="35"/>
       <c r="H44" s="36"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="74"/>
-      <c r="B45" s="74"/>
+      <c r="A45" s="80"/>
+      <c r="B45" s="80"/>
       <c r="C45" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E45" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="74"/>
-      <c r="B46" s="74"/>
+      <c r="A46" s="80"/>
+      <c r="B46" s="80"/>
       <c r="C46" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D46" s="85"/>
-      <c r="E46" s="86"/>
-      <c r="F46" s="87"/>
-      <c r="G46" s="87"/>
-      <c r="H46" s="88"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="82"/>
+      <c r="F46" s="83"/>
+      <c r="G46" s="83"/>
+      <c r="H46" s="84"/>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="74"/>
-      <c r="B47" s="74" t="s">
+      <c r="A47" s="80"/>
+      <c r="B47" s="80" t="s">
         <v>55</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F47" s="34"/>
       <c r="G47" s="35"/>
       <c r="H47" s="36"/>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="74"/>
-      <c r="B48" s="74"/>
+      <c r="A48" s="80"/>
+      <c r="B48" s="80"/>
       <c r="C48" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G48" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="74"/>
-      <c r="B49" s="74"/>
+      <c r="A49" s="80"/>
+      <c r="B49" s="80"/>
       <c r="C49" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D49" s="85"/>
-      <c r="E49" s="86"/>
-      <c r="F49" s="87"/>
-      <c r="G49" s="87"/>
-      <c r="H49" s="88"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="84"/>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="74"/>
-      <c r="B50" s="74" t="s">
+      <c r="A50" s="80"/>
+      <c r="B50" s="80" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F50" s="34"/>
       <c r="G50" s="35"/>
       <c r="H50" s="36"/>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="74"/>
-      <c r="B51" s="74"/>
+      <c r="A51" s="80"/>
+      <c r="B51" s="80"/>
       <c r="C51" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D51" s="33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E51" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F51" s="38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G51" s="38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H51" s="38" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="74"/>
-      <c r="B52" s="74"/>
+      <c r="A52" s="80"/>
+      <c r="B52" s="80"/>
       <c r="C52" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="89"/>
-      <c r="E52" s="90"/>
-      <c r="F52" s="90"/>
-      <c r="G52" s="90"/>
-      <c r="H52" s="91"/>
+      <c r="D52" s="91"/>
+      <c r="E52" s="92"/>
+      <c r="F52" s="92"/>
+      <c r="G52" s="92"/>
+      <c r="H52" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D25:H25"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="A2:A3"/>
@@ -7414,27 +7428,6 @@
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7453,592 +7446,575 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" thickBot="1">
       <c r="A1" s="26" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="96" t="s">
-        <v>319</v>
-      </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="98"/>
+      <c r="B2" s="105" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="107"/>
     </row>
     <row r="3" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A3" s="110"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="101"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110"/>
     </row>
     <row r="4" spans="1:7" ht="17.25">
       <c r="A4" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C4" s="92" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="92"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
+        <v>325</v>
+      </c>
+      <c r="C4" s="94" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="109" t="s">
+      <c r="A5" s="97" t="s">
         <v>77</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="11"/>
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" ht="33">
-      <c r="A6" s="109"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="109"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="105"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="102"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="97" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
       <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:7" ht="33">
-      <c r="A9" s="109"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="109"/>
+      <c r="A10" s="97"/>
       <c r="B10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="105"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="102"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="97" t="s">
         <v>84</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
       <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" ht="33">
-      <c r="A12" s="109"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>327</v>
-      </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="109"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="105"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="102"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="109" t="s">
+      <c r="A14" s="97" t="s">
         <v>87</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="18"/>
       <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="109"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="4" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="109"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="108"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="104"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="97" t="s">
         <v>89</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:7" ht="33">
-      <c r="A18" s="109"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="109"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="105"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="102"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="109" t="s">
+      <c r="A20" s="97" t="s">
         <v>93</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="11"/>
       <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7" ht="33">
-      <c r="A21" s="109"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="109"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="102"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="105"/>
+      <c r="C22" s="98"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="102"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="109" t="s">
+      <c r="A23" s="97" t="s">
         <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>98</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="109"/>
+      <c r="A24" s="97"/>
       <c r="B24" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="109"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="102"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="105"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="102"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="109" t="s">
+      <c r="A26" s="97" t="s">
         <v>101</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
     </row>
     <row r="27" spans="1:7" ht="33">
-      <c r="A27" s="109"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="109"/>
+      <c r="A28" s="97"/>
       <c r="B28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="102"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="105"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="102"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="109" t="s">
+      <c r="A29" s="97" t="s">
         <v>105</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="11"/>
       <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:7" ht="33">
-      <c r="A30" s="109"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="109"/>
+      <c r="A31" s="97"/>
       <c r="B31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="102"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="105"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="102"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="109" t="s">
+      <c r="A32" s="97" t="s">
         <v>108</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="11"/>
       <c r="G32" s="12"/>
     </row>
     <row r="33" spans="1:7" ht="33">
-      <c r="A33" s="109"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="31.5">
-      <c r="A34" s="109"/>
+      <c r="A34" s="97"/>
       <c r="B34" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="104"/>
-      <c r="G34" s="105"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="102"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="109" t="s">
+      <c r="A35" s="97" t="s">
         <v>112</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="11"/>
       <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7" ht="33">
-      <c r="A36" s="109"/>
+      <c r="A36" s="97"/>
       <c r="B36" s="4" t="s">
         <v>114</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="109"/>
+      <c r="A37" s="97"/>
       <c r="B37" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="102"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="106"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="B2:G3"/>
     <mergeCell ref="C25:G25"/>
     <mergeCell ref="C28:G28"/>
@@ -8047,6 +8023,23 @@
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8066,39 +8059,39 @@
   <sheetData>
     <row r="1" spans="1:12" ht="38.25" customHeight="1" thickBot="1">
       <c r="A1" s="26" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
+      <c r="K2" s="106"/>
       <c r="L2" s="59"/>
     </row>
     <row r="3" spans="1:12" ht="17.25" thickBot="1">
-      <c r="A3" s="110"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="100"/>
-      <c r="J3" s="100"/>
-      <c r="K3" s="100"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
       <c r="L3" s="60"/>
     </row>
     <row r="4" spans="1:12">
@@ -8108,83 +8101,83 @@
       <c r="B4" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="114" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115"/>
+      <c r="C4" s="123" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="124"/>
+      <c r="J4" s="124"/>
+      <c r="K4" s="124"/>
       <c r="L4" s="58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="46.15" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="89" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="89" t="s">
-        <v>221</v>
-      </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="91"/>
+        <v>156</v>
+      </c>
+      <c r="C5" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="91" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="93"/>
       <c r="L5" s="66"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="111" t="s">
         <v>117</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="117"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="115"/>
       <c r="L6" s="66"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="118"/>
+      <c r="A7" s="111"/>
       <c r="B7" s="7" t="s">
         <v>119</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="H7" s="14" t="s">
         <v>244</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>248</v>
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="11"/>
@@ -8192,15 +8185,15 @@
       <c r="L7" s="66"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="118"/>
+      <c r="A8" s="111"/>
       <c r="B8" s="7" t="s">
         <v>120</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
@@ -8212,49 +8205,49 @@
       <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="118"/>
+      <c r="A9" s="111"/>
       <c r="B9" s="7" t="s">
         <v>121</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="H9" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="I9" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="J9" s="17" t="s">
         <v>311</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>315</v>
-      </c>
       <c r="K9" s="17" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="L9" s="66"/>
     </row>
-    <row r="10" spans="1:12" ht="49.5">
-      <c r="A10" s="118"/>
+    <row r="10" spans="1:12" ht="31.5">
+      <c r="A10" s="111"/>
       <c r="B10" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>316</v>
+        <v>420</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="11"/>
@@ -8263,76 +8256,72 @@
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
       <c r="K10" s="12"/>
-      <c r="L10" s="67" t="s">
-        <v>317</v>
-      </c>
+      <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="120" t="s">
+      <c r="A11" s="113" t="s">
         <v>122</v>
       </c>
       <c r="B11" s="40" t="s">
         <v>123</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H11" s="44"/>
       <c r="I11" s="45"/>
       <c r="J11" s="45"/>
       <c r="K11" s="46"/>
-      <c r="L11" s="111" t="s">
-        <v>330</v>
-      </c>
+      <c r="L11" s="120"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="120"/>
+      <c r="A12" s="113"/>
       <c r="B12" s="40" t="s">
         <v>124</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G12" s="48" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H12" s="49"/>
       <c r="I12" s="50"/>
       <c r="J12" s="50"/>
       <c r="K12" s="51"/>
-      <c r="L12" s="112"/>
+      <c r="L12" s="121"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="120"/>
+      <c r="A13" s="113"/>
       <c r="B13" s="40" t="s">
         <v>125</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E13" s="49"/>
       <c r="F13" s="50"/>
@@ -8341,47 +8330,47 @@
       <c r="I13" s="53"/>
       <c r="J13" s="53"/>
       <c r="K13" s="54"/>
-      <c r="L13" s="112"/>
+      <c r="L13" s="121"/>
     </row>
     <row r="14" spans="1:12" ht="33">
-      <c r="A14" s="120"/>
+      <c r="A14" s="113"/>
       <c r="B14" s="40" t="s">
         <v>126</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G14" s="55" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H14" s="44"/>
       <c r="I14" s="48"/>
       <c r="J14" s="53"/>
       <c r="K14" s="54"/>
-      <c r="L14" s="112"/>
+      <c r="L14" s="121"/>
     </row>
     <row r="15" spans="1:12" ht="29.65" customHeight="1">
-      <c r="A15" s="120"/>
+      <c r="A15" s="113"/>
       <c r="B15" s="40" t="s">
         <v>127</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F15" s="48"/>
       <c r="G15" s="48"/>
@@ -8389,18 +8378,18 @@
       <c r="I15" s="53"/>
       <c r="J15" s="53"/>
       <c r="K15" s="54"/>
-      <c r="L15" s="112"/>
+      <c r="L15" s="121"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="120"/>
+      <c r="A16" s="113"/>
       <c r="B16" s="40" t="s">
         <v>128</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E16" s="49"/>
       <c r="F16" s="50"/>
@@ -8409,29 +8398,29 @@
       <c r="I16" s="53"/>
       <c r="J16" s="53"/>
       <c r="K16" s="54"/>
-      <c r="L16" s="113"/>
+      <c r="L16" s="122"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="111" t="s">
         <v>129</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>130</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="11"/>
@@ -8440,24 +8429,24 @@
       <c r="L17" s="66"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="118"/>
+      <c r="A18" s="111"/>
       <c r="B18" s="7" t="s">
         <v>131</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="11"/>
@@ -8466,63 +8455,63 @@
       <c r="L18" s="66"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="118"/>
+      <c r="A19" s="111"/>
       <c r="B19" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="89"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="117"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="115"/>
       <c r="L19" s="66"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="118" t="s">
+      <c r="A20" s="111" t="s">
         <v>133</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>134</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="H20" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>275</v>
-      </c>
       <c r="I20" s="14" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="19"/>
       <c r="L20" s="66"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="118"/>
+      <c r="A21" s="111"/>
       <c r="B21" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
@@ -8534,26 +8523,26 @@
       <c r="L21" s="66"/>
     </row>
     <row r="22" spans="1:12" ht="33">
-      <c r="A22" s="118" t="s">
+      <c r="A22" s="111" t="s">
         <v>136</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>137</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="G22" s="21" t="s">
         <v>276</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>280</v>
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="18"/>
@@ -8562,24 +8551,24 @@
       <c r="L22" s="66"/>
     </row>
     <row r="23" spans="1:12" ht="33">
-      <c r="A23" s="118"/>
+      <c r="A23" s="111"/>
       <c r="B23" s="7" t="s">
         <v>138</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>169</v>
-      </c>
       <c r="G23" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="18"/>
@@ -8588,24 +8577,24 @@
       <c r="L23" s="23"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="118"/>
+      <c r="A24" s="111"/>
       <c r="B24" s="7" t="s">
         <v>139</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="14"/>
@@ -8614,24 +8603,24 @@
       <c r="L24" s="23"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="118"/>
+      <c r="A25" s="111"/>
       <c r="B25" s="7" t="s">
         <v>140</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="14"/>
@@ -8640,24 +8629,24 @@
       <c r="L25" s="23"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="118"/>
+      <c r="A26" s="111"/>
       <c r="B26" s="7" t="s">
         <v>141</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
@@ -8666,24 +8655,24 @@
       <c r="L26" s="23"/>
     </row>
     <row r="27" spans="1:12" ht="31.5">
-      <c r="A27" s="118"/>
+      <c r="A27" s="111"/>
       <c r="B27" s="7" t="s">
         <v>142</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G27" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="21"/>
@@ -8692,86 +8681,86 @@
       <c r="L27" s="23"/>
     </row>
     <row r="28" spans="1:12" ht="33">
-      <c r="A28" s="118" t="s">
+      <c r="A28" s="111" t="s">
         <v>143</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>144</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="G28" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="H28" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I28" s="65" t="s">
         <v>297</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I28" s="65" t="s">
-        <v>301</v>
       </c>
       <c r="J28" s="21"/>
       <c r="K28" s="13"/>
       <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" ht="33">
-      <c r="A29" s="118"/>
+      <c r="A29" s="111"/>
       <c r="B29" s="7" t="s">
-        <v>145</v>
+        <v>421</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="H29" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="I29" s="65" t="s">
         <v>297</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I29" s="65" t="s">
-        <v>301</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="13"/>
       <c r="L29" s="23"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="118"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="18"/>
@@ -8780,24 +8769,24 @@
       <c r="L30" s="23"/>
     </row>
     <row r="31" spans="1:12" ht="31.5">
-      <c r="A31" s="118"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="H31" s="21"/>
       <c r="I31" s="10"/>
@@ -8806,24 +8795,24 @@
       <c r="L31" s="23"/>
     </row>
     <row r="32" spans="1:12" ht="31.5">
-      <c r="A32" s="118"/>
+      <c r="A32" s="111"/>
       <c r="B32" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="21"/>
@@ -8832,68 +8821,68 @@
       <c r="L32" s="23"/>
     </row>
     <row r="33" spans="1:12" ht="33">
-      <c r="A33" s="118"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I33" s="10"/>
       <c r="J33" s="10"/>
       <c r="K33" s="12"/>
       <c r="L33" s="23"/>
     </row>
-    <row r="34" spans="1:12" ht="31.5">
-      <c r="A34" s="118"/>
+    <row r="34" spans="1:12">
+      <c r="A34" s="111"/>
       <c r="B34" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="89"/>
-      <c r="D34" s="90"/>
-      <c r="E34" s="90"/>
-      <c r="F34" s="90"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="116"/>
-      <c r="J34" s="116"/>
-      <c r="K34" s="117"/>
+        <v>423</v>
+      </c>
+      <c r="C34" s="91"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="114"/>
+      <c r="K34" s="115"/>
       <c r="L34" s="23"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="118"/>
+      <c r="A35" s="111"/>
       <c r="B35" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="11"/>
@@ -8902,26 +8891,26 @@
       <c r="L35" s="23"/>
     </row>
     <row r="36" spans="1:12" ht="31.5">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="111" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="C36" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="21"/>
@@ -8930,33 +8919,33 @@
       <c r="L36" s="23"/>
     </row>
     <row r="37" spans="1:12" ht="31.5">
-      <c r="A37" s="118"/>
+      <c r="A37" s="111"/>
       <c r="B37" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C37" s="91"/>
+      <c r="D37" s="92"/>
+      <c r="E37" s="114"/>
+      <c r="F37" s="114"/>
+      <c r="G37" s="114"/>
+      <c r="H37" s="114"/>
+      <c r="I37" s="114"/>
+      <c r="J37" s="114"/>
+      <c r="K37" s="115"/>
+      <c r="L37" s="23"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="111" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="89"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="116"/>
-      <c r="J37" s="116"/>
-      <c r="K37" s="117"/>
-      <c r="L37" s="23"/>
-    </row>
-    <row r="38" spans="1:12">
-      <c r="A38" s="118" t="s">
-        <v>154</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="C38" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D38" s="61" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="62"/>
@@ -8968,24 +8957,24 @@
       <c r="L38" s="23"/>
     </row>
     <row r="39" spans="1:12" ht="31.5">
-      <c r="A39" s="118"/>
+      <c r="A39" s="111"/>
       <c r="B39" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="G39" s="8" t="s">
         <v>286</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="G39" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="H39" s="20"/>
       <c r="I39" s="21"/>
@@ -8994,24 +8983,35 @@
       <c r="L39" s="23"/>
     </row>
     <row r="40" spans="1:12" ht="32.25" thickBot="1">
-      <c r="A40" s="119"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="C40" s="121"/>
-      <c r="D40" s="122"/>
-      <c r="E40" s="122"/>
-      <c r="F40" s="122"/>
-      <c r="G40" s="122"/>
-      <c r="H40" s="122"/>
-      <c r="I40" s="122"/>
-      <c r="J40" s="123"/>
-      <c r="K40" s="124"/>
+        <v>424</v>
+      </c>
+      <c r="C40" s="116"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="119"/>
       <c r="L40" s="25"/>
     </row>
     <row r="41" spans="1:12" ht="17.25" thickTop="1"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="L11:L16"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A28:A35"/>
     <mergeCell ref="A36:A37"/>
     <mergeCell ref="A38:A40"/>
     <mergeCell ref="A11:A16"/>
@@ -9020,17 +9020,6 @@
     <mergeCell ref="C37:K37"/>
     <mergeCell ref="C40:K40"/>
     <mergeCell ref="C34:K34"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A28:A35"/>
-    <mergeCell ref="B2:K3"/>
-    <mergeCell ref="L11:L16"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C19:K19"/>
-    <mergeCell ref="G5:K5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
